--- a/summer project 1.1_bom_completed.xlsx
+++ b/summer project 1.1_bom_completed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gvshi\Desktop\tiburon\Summer Project\With LM5050\summer project 1.1\summer project 1.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D8BF978-F392-4341-8C85-E8AF4E27B277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52DA269-206E-4458-9386-9F23F176563C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{16E1177F-9D59-44B7-BFC7-EB632D773ADD}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Id;"Designator";"Footprint";"Quantity";"Designation";"Supplier and ref";</t>
   </si>
@@ -149,6 +149,18 @@
   </si>
   <si>
     <t>0.1u</t>
+  </si>
+  <si>
+    <t>1711725(Phoenix Contact)</t>
+  </si>
+  <si>
+    <t>XT30UPB-F</t>
+  </si>
+  <si>
+    <t>311-100HRCT-ND(Digikey)</t>
+  </si>
+  <si>
+    <t>490-1315-1-ND(Digikey)</t>
   </si>
 </sst>
 </file>
@@ -632,9 +644,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -680,9 +698,18 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -725,15 +752,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7FAEE63-0C37-40DF-B37F-E32367680A4C}" name="summer_project_1_0_bom" displayName="summer_project_1_0_bom" ref="A1:F7" tableType="queryTable" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7FAEE63-0C37-40DF-B37F-E32367680A4C}" name="summer_project_1_0_bom" displayName="summer_project_1_0_bom" ref="A1:F7" tableType="queryTable" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:F7" xr:uid="{C7FAEE63-0C37-40DF-B37F-E32367680A4C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F2C4E7A8-E2B1-4132-8258-8AC2D6944EC3}" uniqueName="1" name="Id" queryTableFieldId="1"/>
-    <tableColumn id="2" xr3:uid="{8D82997A-2F54-4D51-8972-63D932146BDE}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{160C1F7E-92CE-42DA-A226-3EDC0ED5265E}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{06F95B4A-85FA-4439-8A7E-D676A5BCA244}" uniqueName="4" name="Quantity" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{C566C4EB-064E-4E91-953B-38EAB4433062}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{6C088470-7836-4B73-9ADF-B4A1ECF87C59}" uniqueName="7" name="Part Number" queryTableFieldId="7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F2C4E7A8-E2B1-4132-8258-8AC2D6944EC3}" uniqueName="1" name="Id" queryTableFieldId="1" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{8D82997A-2F54-4D51-8972-63D932146BDE}" uniqueName="2" name="Designator" queryTableFieldId="2" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{160C1F7E-92CE-42DA-A226-3EDC0ED5265E}" uniqueName="3" name="Footprint" queryTableFieldId="3" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{06F95B4A-85FA-4439-8A7E-D676A5BCA244}" uniqueName="4" name="Quantity" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C566C4EB-064E-4E91-953B-38EAB4433062}" uniqueName="5" name="Designation" queryTableFieldId="5" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{6C088470-7836-4B73-9ADF-B4A1ECF87C59}" uniqueName="7" name="Part Number" queryTableFieldId="7" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1059,152 +1086,152 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>21</v>
+      <c r="F5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
+      <c r="F6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
+      <c r="F7" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
